--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486477_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486477_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6526</v>
+        <v>5.8687</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9615</v>
+        <v>2.4176</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3089</v>
+        <v>3.4511</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1933</v>
+        <v>0.2934</v>
       </c>
       <c r="H2" t="n">
-        <v>0.225</v>
+        <v>-2.682</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4184</v>
+        <v>2.9755</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6012</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4594</v>
+        <v>-2.1162</v>
       </c>
       <c r="L2" t="n">
-        <v>0.153</v>
+        <v>2.7173</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8057</v>
+        <v>-0.3077</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2344</v>
+        <v>-0.5659</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5714</v>
+        <v>0.2582</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R2" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6735</v>
+        <v>0.6856</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9167</v>
+        <v>0.0589</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7568</v>
+        <v>0.6267</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3899</v>
+        <v>4.8897</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5199</v>
+        <v>4.1501</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9331</v>
+        <v>4.5419</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7903</v>
+        <v>4.9124</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1428</v>
+        <v>-0.3705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2934</v>
+        <v>-0.1933</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.682</v>
+        <v>0.225</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9755</v>
+        <v>-0.4184</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6012</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.1162</v>
+        <v>0.4594</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7173</v>
+        <v>0.153</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3077</v>
+        <v>-0.8057</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5659</v>
+        <v>-0.2344</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2582</v>
+        <v>-0.5714</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2499</v>
+        <v>1.5628</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5684</v>
+        <v>0.8676</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3184</v>
+        <v>0.6952</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8897</v>
+        <v>3.3899</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1501</v>
+        <v>4.5199</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5504</v>
+        <v>2.8549</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9523</v>
+        <v>2.2876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5981</v>
+        <v>0.5673</v>
       </c>
       <c r="G4" t="n">
         <v>1.5177</v>
@@ -766,13 +766,13 @@
         <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4024</v>
+        <v>0.7069</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3305</v>
+        <v>0.0048</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7329</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5243</v>
+        <v>2.009</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0313</v>
+        <v>0.5468</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4931</v>
+        <v>1.4622</v>
       </c>
       <c r="G5" t="n">
         <v>0.2486</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2534</v>
+        <v>0.7381</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7859</v>
+        <v>-0.2704</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0393</v>
+        <v>1.0085</v>
       </c>
       <c r="V5" t="n">
         <v>0.3698</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6784</v>
+        <v>0.0191</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6747</v>
+        <v>-1.894</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3531</v>
+        <v>1.9131</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.134</v>
+        <v>-2.052</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1404</v>
+        <v>-1.1221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0064</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1571</v>
+        <v>-2.0758</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5896</v>
+        <v>-0.7387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7467</v>
+        <v>-1.3371</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2911</v>
+        <v>0.0238</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5508</v>
+        <v>-0.3834</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7403</v>
+        <v>0.4072</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7694</v>
+        <v>0.9836</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3003</v>
+        <v>0.3569</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4692</v>
+        <v>0.6267</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2129</v>
+        <v>-0.0309</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.9276</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2129</v>
+        <v>-0.9585</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2335</v>
+        <v>-1.0628</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.5664</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2335</v>
+        <v>0.5036</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.7558</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3914</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2335</v>
+        <v>-2.8187</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2335</v>
+        <v>-1.8878</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0205</v>
+        <v>1.0542</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.2392</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0205</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4694</v>
+        <v>-0.1821</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0742</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6048</v>
+        <v>-0.1821</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.052</v>
+        <v>-0.2335</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1221</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.2335</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0758</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7387</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3371</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0238</v>
+        <v>-0.2335</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3834</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4072</v>
+        <v>-0.2335</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4951</v>
+        <v>0.0514</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1767</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3184</v>
+        <v>0.0514</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5474</v>
+        <v>-0.494</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2571</v>
+        <v>-2.7238</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8044</v>
+        <v>2.2298</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0628</v>
+        <v>-1.134</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5664</v>
+        <v>-1.1404</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5036</v>
+        <v>0.0064</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7558</v>
+        <v>0.1571</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5896</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3914</v>
+        <v>0.7467</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8187</v>
+        <v>-1.2911</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.5508</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8878</v>
+        <v>-0.7403</v>
       </c>
       <c r="P9" t="n">
         <v>-0.2175</v>
@@ -1156,22 +1156,22 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.5971</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4314</v>
+        <v>0.2512</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9692</v>
+        <v>1.3459</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3252</v>
+        <v>-0.7395</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0794</v>
+        <v>-2.6227</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2017</v>
+        <v>-0.3135</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8777</v>
+        <v>-2.3093</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7305</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5413</v>
+        <v>0.998</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1971</v>
+        <v>0.0853</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3442</v>
+        <v>0.9127</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0995</v>
+        <v>-2.691</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9779</v>
+        <v>-1.7544</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1216</v>
+        <v>-0.9366</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8612</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3682</v>
+        <v>0.0403</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0428</v>
+        <v>0.2277</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.930199999999999</v>
+        <v>9.2729</v>
       </c>
       <c r="E12" t="n">
-        <v>4.064000000000001</v>
+        <v>4.4063</v>
       </c>
       <c r="F12" t="n">
-        <v>4.866400000000001</v>
+        <v>4.8665</v>
       </c>
       <c r="G12" t="n">
         <v>-7.207599999999999</v>
@@ -1390,13 +1390,13 @@
         <v>13.0505</v>
       </c>
       <c r="S12" t="n">
-        <v>8.0753</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0636</v>
+        <v>1.406</v>
       </c>
       <c r="U12" t="n">
-        <v>7.011699999999999</v>
+        <v>7.011899999999999</v>
       </c>
       <c r="V12" t="n">
         <v>6.9751</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0841</v>
+        <v>4.7528</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2768</v>
+        <v>2.0533</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8074</v>
+        <v>2.6996</v>
       </c>
       <c r="G13" t="n">
         <v>3.5271</v>
@@ -1468,13 +1468,13 @@
         <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>0.13</v>
+        <v>-0.2013</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6249</v>
+        <v>-0.8484</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7549</v>
+        <v>0.6471</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9655</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4922</v>
+        <v>2.3169</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1457</v>
+        <v>2.3692</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6535</v>
+        <v>-0.0523</v>
       </c>
       <c r="G14" t="n">
         <v>3.73</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5003</v>
+        <v>-0.6757</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1644</v>
+        <v>-0.9409</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3359</v>
+        <v>0.2653</v>
       </c>
       <c r="V14" t="n">
         <v>-2.2599</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0187</v>
+        <v>1.6392</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5758</v>
+        <v>2.6876</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5571</v>
+        <v>-1.0484</v>
       </c>
       <c r="G15" t="n">
         <v>3.3924</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.848</v>
+        <v>-1.2275</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2329</v>
+        <v>-1.1212</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.615</v>
+        <v>-0.1064</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3082</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0211</v>
+        <v>0.3681</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2342</v>
+        <v>-0.1011</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2553</v>
+        <v>0.4692</v>
       </c>
       <c r="G16" t="n">
         <v>1.301</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6611</v>
+        <v>-0.2719</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2139</v>
+        <v>-0.5492</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4472</v>
+        <v>0.2773</v>
       </c>
       <c r="V16" t="n">
         <v>-0.226</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8136</v>
+        <v>-0.8084</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.152</v>
+        <v>-1.2505</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3384</v>
+        <v>0.4421</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.091</v>
+        <v>1.7478</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4957</v>
+        <v>1.1342</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4048</v>
+        <v>0.6136</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5356</v>
+        <v>1.508</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7268</v>
+        <v>0.1095</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1912</v>
+        <v>1.3985</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4446</v>
+        <v>0.2398</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2311</v>
+        <v>1.0247</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2136</v>
+        <v>-0.7849</v>
       </c>
       <c r="P17" t="n">
         <v>-0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1559</v>
+        <v>-0.8559</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4711</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3152</v>
+        <v>-0.0772</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.226</v>
+        <v>-1.0477</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.226</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9649</v>
+        <v>-1.119</v>
       </c>
       <c r="E18" t="n">
         <v>0.858</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8229</v>
+        <v>-1.977</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2459</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1712</v>
+        <v>0.0171</v>
       </c>
       <c r="T18" t="n">
         <v>-0.411</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.4281</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3252</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3723</v>
+        <v>-1.2041</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3623</v>
+        <v>-1.5991</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.01</v>
+        <v>0.395</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7478</v>
+        <v>-0.091</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1342</v>
+        <v>-0.4957</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6136</v>
+        <v>0.4048</v>
       </c>
       <c r="J19" t="n">
-        <v>1.508</v>
+        <v>-0.5356</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1095</v>
+        <v>-0.7268</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3985</v>
+        <v>0.1912</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2398</v>
+        <v>0.4446</v>
       </c>
       <c r="N19" t="n">
-        <v>1.0247</v>
+        <v>0.2311</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7849</v>
+        <v>0.2136</v>
       </c>
       <c r="P19" t="n">
         <v>-0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4198</v>
+        <v>-0.2346</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8904</v>
+        <v>0.024</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5294</v>
+        <v>-0.2587</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0477</v>
+        <v>-0.226</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.243</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2805</v>
+        <v>-2.1597</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8476</v>
+        <v>-2.624</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4643</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6913</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2587</v>
+        <v>-0.1379</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9589</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7002</v>
+        <v>0.5975</v>
       </c>
       <c r="V20" t="n">
         <v>-0.113</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4776</v>
+        <v>-3.0011</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3504</v>
+        <v>-2.2387</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1272</v>
+        <v>-0.7624</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6467000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2177</v>
+        <v>-0.7411</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6012</v>
+        <v>-0.2364</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3082</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5953</v>
+        <v>-6.7347</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2445</v>
+        <v>-5.021</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3508</v>
+        <v>-1.7137</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8156</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.627</v>
+        <v>-0.7664</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3699</v>
+        <v>-1.1464</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2571</v>
+        <v>0.38</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.930299999999999</v>
+        <v>-5.950000000000002</v>
       </c>
       <c r="E23" t="n">
         <v>-4.866300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.064</v>
+        <v>-1.0836</v>
       </c>
       <c r="G23" t="n">
         <v>7.207799999999999</v>
@@ -2248,13 +2248,13 @@
         <v>11.9627</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.0755</v>
+        <v>-5.0952</v>
       </c>
       <c r="T23" t="n">
-        <v>-7.011700000000001</v>
+        <v>-7.011899999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0637</v>
+        <v>1.9166</v>
       </c>
       <c r="V23" t="n">
         <v>-6.9749</v>
